--- a/Du lieu Dashboard PVEP SH.xlsx
+++ b/Du lieu Dashboard PVEP SH.xlsx
@@ -16,6 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RuiRo" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DichVu" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TuanThu" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DoanhThu" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuDap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="XoaLo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="XoaLoNam" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -24,9 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00;\-#,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -156,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +189,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="2"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -562,9 +569,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -579,9 +583,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
@@ -631,9 +632,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -669,9 +667,6 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
@@ -686,9 +681,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
@@ -721,6 +713,97 @@
       <c r="A27" t="inlineStr">
         <is>
           <t>• Các sheet này thêm/bớt dòng tự do, giữ nguyên thứ tự cột và dòng tiêu đề.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>── DOANHTHU (cập nhật khi có số BCTC quý hoặc số cộng dồn mới) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>• Cột Mã cha–con như TienDo (1 → 1.1). Dòng cha để TRỐNG 4 cột số — dashboard tự CỘNG từ dịch vụ con.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>• KH HĐTV giao = kế hoạch chính thức · KH quản trị = kế hoạch phấn đấu · TH theo BCTC = lũy kế theo BCTC quý gần nhất · TH đến nay = cộng dồn đến thời điểm cập nhật (kể cả chưa lên BCTC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>• Số hiện tại là SỐ MINH HỌA — thay bằng số thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>── BUDAP (việc cần triển khai để bù đắp nếu hụt KH) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>• Mỗi dòng 1 giải pháp: nội dung / mảng / tác động dự kiến (tỷ) / hạn / đèn r-a-g. Hiện ở tab Doanh thu + cockpit Lãnh đạo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>── XOALO (kế hoạch xóa lỗ lũy kế đến 2029) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>• Loại KH: HĐTV = kế hoạch được HĐTV giao · QT = kế hoạch quản trị. Bấm thẻ "Mục tiêu xóa lỗ 2029" trên dashboard để xem danh sách này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>── CHẾ ĐỘ KHÁCH ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>• Nút "Khách" ở góc phải: trang giới thiệu dịch vụ, ẨN toàn bộ tab số liệu. LƯU Ý: chỉ dùng để TRÌNH CHIẾU — không gửi file index.html cho khách (dữ liệu vẫn nằm trong mã nguồn trang).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>── XOALONAM (chỉ tiêu DT/LN từng năm để xóa lỗ đến 2029) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>• Mỗi năm 1 dòng: DT KH / LN KH HĐTV / LN KH quản trị / lỗ lũy kế còn lại mục tiêu cuối năm / tình hình. Hiện trong cửa sổ "Mục tiêu xóa lỗ 2029" khi bấm thẻ trên dashboard.</t>
         </is>
       </c>
     </row>
@@ -861,6 +944,1012 @@
           <t>b</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Dịch vụ</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>KH HĐTV giao (tỷ)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>KH quản trị (tỷ)</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>TH theo BCTC (tỷ)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>TH đến nay (tỷ)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Thương mại &amp; phân phối (than, MMO, xăng dầu)</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>Dòng cha — dashboard tự cộng từ dịch vụ con</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Kinh doanh than (PVPower)</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — chờ GP &amp; HĐ, dự kiến từ cuối T6/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Cung cấp MMO (PVOil)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — chờ ký hợp đồng</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Kinh doanh xăng dầu</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>205</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — chờ giấy phép + thuê cửa hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Dịch vụ kỹ thuật</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Dịch vụ CCS</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>G&amp;G / nhập liệu ITC</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>HWU / thử vỉa</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — chờ chủ trương đầu tư</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Hỗ trợ sản xuất &amp; XNK</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Tổ chức sự kiện &amp; truyền thông</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — mảng biên thấp, đang thu hẹp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Khu lưu niệm Thái Bình &amp; khác</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Việc cần triển khai để bù đắp</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Tác động dự kiến (tỷ)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Hạn</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Đèn (r/a/g)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Đẩy nhanh GP xăng dầu + bổ sung ngành nghề để bán than/MMO từ T7 (thay vì T9)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Thương mại</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>31/7/2026</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Nút thắt lớn nhất của KH năm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Ký sớm HĐ than PVPower — chốt khối lượng Quý 3–4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Thương mại</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>15/8/2026</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Chốt 2 hợp đồng CCS đang đàm phán</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>DV kỹ thuật</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>30/9/2026</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Tăng kíp nhập liệu ITC (thêm 1 ca)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>DV kỹ thuật</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>31/8/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Thu hẹp mảng sự kiện biên thấp, dồn nhân lực sang DV kỹ thuật</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Danh mục</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>30/9/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Tác động vào lợi nhuận nhiều hơn doanh thu</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Nhiệm vụ</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Loại KH (HĐTV / QT)</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Mốc hoàn thành</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Tình hình thực hiện</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Đèn (r/a/g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Xử lý dứt điểm lỗ lũy kế trước 31/12/2029</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>HĐTV</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>31/12/2029</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Đã xử lý 1,82/19,15 tỷ (~9%)</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Không phát sinh lỗ mới từ 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>HĐTV</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Hằng năm</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Quý I/2026 lãi +0,29 tỷ</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Hoàn thành KH doanh thu &amp; lợi nhuận 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>HĐTV</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Mới đạt ~0,6% KH doanh thu năm</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Thoát diện giám sát tài chính đặc biệt (QĐ 2259)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>HĐTV</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Đang trong diện giám sát</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Giải tỏa 28 tỷ tiền gửi phong tỏa MBV</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>QT</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>2026–2027</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>~10% — bám lộ trình Petrovietnam</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Thu hồi ~30 tỷ tạm ứng DAĐH &amp; thanh lý HĐ điều hành</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>QT</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>~15% — P.TCKT chủ trì</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Xử lý công nợ ZJ15 + trích lập bổ sung 2,5 tỷ</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>QT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>30/6/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>~40% — theo ý kiến kiểm toán</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Tái cơ cấu danh mục dịch vụ (thu hẹp sự kiện, tăng kỹ thuật)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>QT</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>~25% — đang dịch chuyển</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Tiết giảm chi phí quản lý doanh nghiệp ≥ 10%</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>QT</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Hằng năm</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát định mức</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Năm</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>DT kế hoạch (tỷ)</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>LN KH HĐTV giao (tỷ)</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>LN KH quản trị (tỷ)</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Lỗ lũy kế còn lại mục tiêu (tỷ)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Tình hình thực hiện</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Đèn (r/a/g, trống = chưa tới)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2" s="20" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Quý I lãi +0,29 tỷ (~15% KH LN năm)</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA — thay bằng KH thật</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>SỐ MINH HỌA</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Xóa hết lỗ — đủ điều kiện cổ phần hóa 2030</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
